--- a/artfynd/S 461-2023 artfynd.xlsx
+++ b/artfynd/S 461-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/145705</t>
         </is>
       </c>
     </row>
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92513612</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1006,6 +1021,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/312214</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1112,6 +1132,11 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/315892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Inventering av Ölands kärlväxtflora., Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/390046</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1352,6 +1382,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/390062</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1475,6 +1510,11 @@
       <c r="AY8" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80711320</t>
         </is>
       </c>
     </row>
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/459954</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1702,6 +1747,11 @@
       <c r="AY10" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/423969</t>
         </is>
       </c>
     </row>
@@ -1814,6 +1864,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66625608</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
       <c r="AY12" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106126329</t>
         </is>
       </c>
     </row>
@@ -2051,6 +2111,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114983076</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2172,6 +2237,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2218034</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2291,6 +2361,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130575409</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2410,6 +2485,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130575375</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2518,6 +2598,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64366887</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2637,6 +2722,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133928509</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2756,6 +2846,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133928520</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2863,6 +2958,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116591141</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2989,6 +3089,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63201330</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3105,6 +3210,11 @@
           <t>Inventering av långbensgroda</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59024153</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3214,6 +3324,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7245113</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3324,6 +3439,11 @@
           <t>Inventering av långbensgroda</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62369747</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3438,6 +3558,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17241923</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3581,6 +3706,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115676475</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3721,6 +3851,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115234924</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3841,6 +3976,11 @@
           <t>Ekoxeuppropet 2020</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98337019</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3966,6 +4106,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110074495</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4076,6 +4221,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102671488</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4183,6 +4333,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108523610</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4302,6 +4457,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132960594</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4425,6 +4585,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132960597</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4544,6 +4709,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130776954</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4652,6 +4822,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64366891</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4763,6 +4938,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113486110</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4889,6 +5069,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202691</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5015,6 +5200,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189721</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5141,6 +5331,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63228705</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5259,6 +5454,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70536745</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5376,6 +5576,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7245115</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5487,6 +5692,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2150014</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5598,6 +5808,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2303613</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5709,6 +5924,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773262</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5824,6 +6044,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2635842</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5935,6 +6160,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2676226</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6049,6 +6279,11 @@
       <c r="AY47" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2485505</t>
         </is>
       </c>
     </row>
@@ -6162,6 +6397,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78870732</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6273,6 +6513,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78870901</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6379,6 +6624,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131574560</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6485,6 +6735,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3440372</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6600,6 +6855,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118348</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6710,6 +6970,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118349</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6820,6 +7085,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106118350</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6931,6 +7201,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3367715</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7035,6 +7310,11 @@
       <c r="AY56" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5024204</t>
         </is>
       </c>
     </row>
@@ -7144,6 +7424,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92513455</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7255,6 +7540,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773215</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7366,6 +7656,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773205</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7477,6 +7772,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773199</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7586,6 +7886,11 @@
       <c r="AY61" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5462704</t>
         </is>
       </c>
     </row>
@@ -7704,6 +8009,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77033617</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7815,6 +8125,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92513436</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7921,6 +8236,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100502889</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8031,6 +8351,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106121031</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8137,6 +8462,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5779785</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8251,6 +8581,11 @@
       <c r="AY67" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5784861</t>
         </is>
       </c>
     </row>
@@ -8362,6 +8697,11 @@
       <c r="AY68" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78870855</t>
         </is>
       </c>
     </row>
@@ -8476,6 +8816,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78870864</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8578,6 +8923,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6453177</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8697,6 +9047,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130575404</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8816,6 +9171,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773213</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8927,8 +9287,87 @@
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6558759</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 461-2023 artfynd.xlsx
+++ b/artfynd/S 461-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ73"/>
+  <dimension ref="A1:AZ74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4114,10 +4114,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102671488</v>
+        <v>136151060</v>
       </c>
       <c r="B30" t="n">
-        <v>58438</v>
+        <v>9417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4125,45 +4125,41 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102625</v>
+        <v>101246</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Halsbandsflugsnappare</t>
+          <t>Ekoxe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ficedula albicollis</t>
+          <t>Lucanus cervus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Temminck, 1795)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592578</v>
+        <v>592592</v>
       </c>
       <c r="R30" t="n">
-        <v>6277661</v>
+        <v>6277698</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4187,17 +4183,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-05-01</t>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Vid holk</t>
+          <t>hona</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4212,24 +4218,24 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Margareta Ohné</t>
+          <t>Monika Sunhede</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Margareta Ohné</t>
+          <t>Via Monika Sunhede</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102671488</t>
+          <t>https://artportalen.se/Sighting/136151060</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>108523610</v>
+        <v>102671488</v>
       </c>
       <c r="B31" t="n">
         <v>58438</v>
@@ -4258,29 +4264,27 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592556</v>
+        <v>592578</v>
       </c>
       <c r="R31" t="n">
-        <v>6277579</v>
+        <v>6277661</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4304,12 +4308,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2022-05-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2022-05-01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Vid holk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4324,27 +4333,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Margareta Ohné</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ward Tamsyn</t>
+          <t>Margareta Ohné</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108523610</t>
+          <t>https://artportalen.se/Sighting/102671488</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132960594</v>
+        <v>108523610</v>
       </c>
       <c r="B32" t="n">
-        <v>58460</v>
+        <v>58438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4369,32 +4378,30 @@
           <t>(Temminck, 1795)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tors lund, Torslunda kyrka, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592443</v>
+        <v>592556</v>
       </c>
       <c r="R32" t="n">
-        <v>6277812</v>
+        <v>6277579</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4418,22 +4425,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>11:05</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>12:06</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4448,24 +4445,24 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Olle Thyrestam</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Olle Thyrestam, Katarina Thyrestam</t>
+          <t>Ward Tamsyn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132960594</t>
+          <t>https://artportalen.se/Sighting/108523610</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132960597</v>
+        <v>132960594</v>
       </c>
       <c r="B33" t="n">
         <v>58460</v>
@@ -4495,18 +4492,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4516,13 +4509,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592584</v>
+        <v>592443</v>
       </c>
       <c r="R33" t="n">
-        <v>6277695</v>
+        <v>6277812</v>
       </c>
       <c r="S33" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4587,66 +4580,70 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132960597</t>
+          <t>https://artportalen.se/Sighting/132960594</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130776954</v>
+        <v>132960597</v>
       </c>
       <c r="B34" t="n">
-        <v>57238</v>
+        <v>58460</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102972</v>
+        <v>102625</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Turkduva</t>
+          <t>Halsbandsflugsnappare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Streptopelia decaocto</t>
+          <t>Ficedula albicollis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Frivaldszky, 1838)</t>
+          <t>(Temminck, 1795)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>rastande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogsby, Öl</t>
+          <t>Tors lund, Torslunda kyrka, Öl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592512</v>
+        <v>592584</v>
       </c>
       <c r="R34" t="n">
-        <v>6277542</v>
+        <v>6277695</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4670,22 +4667,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4700,76 +4697,77 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Bengt E Larsson</t>
+          <t>Olle Thyrestam</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Bengt E Larsson</t>
+          <t>Olle Thyrestam, Katarina Thyrestam</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130776954</t>
+          <t>https://artportalen.se/Sighting/132960597</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>64366891</v>
+        <v>130776954</v>
       </c>
       <c r="B35" t="n">
-        <v>58353</v>
+        <v>57238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103037</v>
+        <v>102972</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Turkduva</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Streptopelia decaocto</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Frivaldszky, 1838)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Skogsby, Öl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592510</v>
+        <v>592512</v>
       </c>
       <c r="R35" t="n">
-        <v>6277534</v>
+        <v>6277542</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4793,12 +4791,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2017-03-11</t>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2017-03-11</t>
+          <t>2026-01-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4813,44 +4821,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Claes Möllersten</t>
+          <t>Bengt E Larsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Claes Möllersten</t>
+          <t>Bengt E Larsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/64366891</t>
+          <t>https://artportalen.se/Sighting/130776954</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113486110</v>
+        <v>64366891</v>
       </c>
       <c r="B36" t="n">
-        <v>58676</v>
+        <v>58353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103055</v>
+        <v>103037</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4860,7 +4868,14 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4869,13 +4884,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592557</v>
+        <v>592510</v>
       </c>
       <c r="R36" t="n">
-        <v>6277543</v>
+        <v>6277534</v>
       </c>
       <c r="S36" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4899,22 +4914,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:29</t>
+          <t>2017-03-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-12-02</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2017-03-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4929,89 +4934,69 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Claes Möllersten</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Pav Johnsson</t>
+          <t>Claes Möllersten</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113486110</t>
+          <t>https://artportalen.se/Sighting/64366891</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>63202691</v>
+        <v>113486110</v>
       </c>
       <c r="B37" t="n">
-        <v>56835</v>
+        <v>58676</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>205995</v>
+        <v>103055</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>autobox med höghastighetsinspelning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Skogsby, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592550</v>
+        <v>592557</v>
       </c>
       <c r="R37" t="n">
-        <v>6277499</v>
+        <v>6277543</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5035,17 +5020,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2012-07-07</t>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2012-07-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>lokal-ID: 3  Box-ID: 3M</t>
+          <t>2023-12-02</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5060,54 +5050,54 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Alexander Eriksson</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Alexander Eriksson, Johnny de Jong</t>
+          <t>Pav Johnsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63202691</t>
+          <t>https://artportalen.se/Sighting/113486110</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>63189721</v>
+        <v>63202691</v>
       </c>
       <c r="B38" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5202,16 +5192,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63189721</t>
+          <t>https://artportalen.se/Sighting/63202691</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>63228705</v>
+        <v>63189721</v>
       </c>
       <c r="B39" t="n">
-        <v>56837</v>
+        <v>56816</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5219,26 +5209,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>113</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5333,33 +5323,33 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/63228705</t>
+          <t>https://artportalen.se/Sighting/63189721</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>70536745</v>
+        <v>63228705</v>
       </c>
       <c r="B40" t="n">
-        <v>58826</v>
+        <v>56837</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208242</v>
+        <v>206002</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5369,12 +5359,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>registreringar</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -5382,23 +5372,26 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>autobox med höghastighetsinspelning</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Damm 2 Torslunda v, Öl</t>
+          <t>Skogsby, Öl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>592541</v>
+        <v>592550</v>
       </c>
       <c r="R40" t="n">
-        <v>6277589</v>
+        <v>6277499</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5425,12 +5418,17 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2018-04-09</t>
+          <t>2012-07-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2018-04-09</t>
+          <t>2012-07-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>lokal-ID: 3  Box-ID: 3M</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5445,27 +5443,27 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Carl-Johan Månsson</t>
+          <t>Alexander Eriksson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Carl-Johan Månsson</t>
+          <t>Alexander Eriksson, Johnny de Jong</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70536745</t>
+          <t>https://artportalen.se/Sighting/63228705</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>7245115</v>
+        <v>70536745</v>
       </c>
       <c r="B41" t="n">
-        <v>58790</v>
+        <v>58826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5473,16 +5471,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5492,7 +5490,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5506,9 +5504,10 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>funnen död</t>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5547,12 +5546,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2014-04-03</t>
+          <t>2018-04-09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2014-04-03</t>
+          <t>2018-04-09</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5578,16 +5577,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7245115</t>
+          <t>https://artportalen.se/Sighting/70536745</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2150014</v>
+        <v>7245115</v>
       </c>
       <c r="B42" t="n">
-        <v>111175</v>
+        <v>58790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5595,42 +5594,57 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>219677</v>
+        <v>208245</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>funnen död</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Damm 2 Torslunda v, Öl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>592473</v>
+        <v>592541</v>
       </c>
       <c r="R42" t="n">
-        <v>6277817</v>
+        <v>6277589</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5654,12 +5668,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2007-02-26</t>
+          <t>2014-04-03</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2007-02-26</t>
+          <t>2014-04-03</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5670,40 +5684,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Carl-Johan Månsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Carl-Johan Månsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2150014</t>
+          <t>https://artportalen.se/Sighting/7245115</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2303613</v>
+        <v>2150014</v>
       </c>
       <c r="B43" t="n">
-        <v>99142</v>
+        <v>111175</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5711,27 +5716,27 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219847</v>
+        <v>219677</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5740,13 +5745,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>592474</v>
+        <v>592473</v>
       </c>
       <c r="R43" t="n">
-        <v>6277717</v>
+        <v>6277817</v>
       </c>
       <c r="S43" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5770,12 +5775,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
+          <t>2007-02-26</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
+          <t>2007-02-26</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5800,7 +5805,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
@@ -5810,16 +5815,16 @@
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2303613</t>
+          <t>https://artportalen.se/Sighting/2150014</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131773262</v>
+        <v>2303613</v>
       </c>
       <c r="B44" t="n">
-        <v>100815</v>
+        <v>99142</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5827,45 +5832,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>219851</v>
+        <v>219847</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hässlebrodd</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Milium effusum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>592576</v>
+        <v>592474</v>
       </c>
       <c r="R44" t="n">
-        <v>6277673</v>
+        <v>6277717</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5889,12 +5891,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5903,39 +5905,42 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>hassel och grova ekar, en del klibbal</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131773262</t>
+          <t>https://artportalen.se/Sighting/2303613</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2635842</v>
+        <v>131773262</v>
       </c>
       <c r="B45" t="n">
-        <v>99141</v>
+        <v>100815</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5943,46 +5948,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219862</v>
+        <v>219851</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Hässlebrodd</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Milium effusum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>592474</v>
+        <v>592576</v>
       </c>
       <c r="R45" t="n">
-        <v>6277717</v>
+        <v>6277673</v>
       </c>
       <c r="S45" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6006,12 +6010,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2006-05-20</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6020,42 +6024,39 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
+          <t>hassel och grova ekar, en del klibbal</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2635842</t>
+          <t>https://artportalen.se/Sighting/131773262</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2676226</v>
+        <v>2635842</v>
       </c>
       <c r="B46" t="n">
-        <v>99147</v>
+        <v>99141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6063,27 +6064,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219864</v>
+        <v>219862</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sankt pers nycklar</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Orchis mascula</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6162,16 +6167,16 @@
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2676226</t>
+          <t>https://artportalen.se/Sighting/2635842</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2485505</v>
+        <v>2676226</v>
       </c>
       <c r="B47" t="n">
-        <v>107718</v>
+        <v>99147</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6179,16 +6184,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220015</v>
+        <v>219864</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hässleklocka</t>
+          <t>Sankt pers nycklar</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Campanula latifolia</t>
+          <t>Orchis mascula</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -6199,22 +6204,22 @@
       <c r="I47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Skogsby, Torslund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>592603</v>
+        <v>592474</v>
       </c>
       <c r="R47" t="n">
-        <v>6277646</v>
+        <v>6277717</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6238,17 +6243,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2007-04-07</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2007-04-07</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Stort bestånd</t>
+          <t>2006-05-20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6268,12 +6268,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Lissbeth Bringer</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Lissbeth Bringer</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
@@ -6283,13 +6283,13 @@
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/2485505</t>
+          <t>https://artportalen.se/Sighting/2676226</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>78870732</v>
+        <v>2485505</v>
       </c>
       <c r="B48" t="n">
         <v>107718</v>
@@ -6318,23 +6318,24 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torslunda kyrka väst, Öl</t>
+          <t>Skogsby, Torslund, Öl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>592597</v>
+        <v>592603</v>
       </c>
       <c r="R48" t="n">
-        <v>6277645</v>
+        <v>6277646</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6358,12 +6359,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2007-04-07</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2007-04-07</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Stort bestånd</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6372,24 +6378,23 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>ädellövskog/skogsstig</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
@@ -6399,13 +6404,13 @@
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78870732</t>
+          <t>https://artportalen.se/Sighting/2485505</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>78870901</v>
+        <v>78870732</v>
       </c>
       <c r="B49" t="n">
         <v>107718</v>
@@ -6440,14 +6445,14 @@
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Torslunda, Öl</t>
+          <t>Torslunda kyrka väst, Öl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>592575</v>
+        <v>592597</v>
       </c>
       <c r="R49" t="n">
-        <v>6277524</v>
+        <v>6277645</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6494,7 +6499,7 @@
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>skogsväg</t>
+          <t>ädellövskog/skogsstig</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6515,16 +6520,16 @@
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78870901</t>
+          <t>https://artportalen.se/Sighting/78870732</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131574560</v>
+        <v>78870901</v>
       </c>
       <c r="B50" t="n">
-        <v>107800</v>
+        <v>107718</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6551,23 +6556,19 @@
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Torslund ost, Öl</t>
+          <t>Torslunda, Öl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>592607</v>
+        <v>592575</v>
       </c>
       <c r="R50" t="n">
-        <v>6277646</v>
+        <v>6277524</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6594,12 +6595,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6612,6 +6613,11 @@
       <c r="AG50" t="b">
         <v>0</v>
       </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>skogsväg</t>
+        </is>
+      </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
@@ -6623,36 +6629,40 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY50" t="inlineStr"/>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131574560</t>
+          <t>https://artportalen.se/Sighting/78870901</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>3440372</v>
+        <v>131574560</v>
       </c>
       <c r="B51" t="n">
-        <v>106812</v>
+        <v>107800</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220785</v>
+        <v>220015</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Hässleklocka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Campanula latifolia</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -6661,19 +6671,27 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Torslund ost, Öl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>592474</v>
+        <v>592607</v>
       </c>
       <c r="R51" t="n">
-        <v>6277717</v>
+        <v>6277646</v>
       </c>
       <c r="S51" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6697,12 +6715,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6711,42 +6729,34 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3440372</t>
+          <t>https://artportalen.se/Sighting/131574560</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>106118348</v>
+        <v>3440372</v>
       </c>
       <c r="B52" t="n">
-        <v>106813</v>
+        <v>106812</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6771,24 +6781,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>592552</v>
+        <v>592474</v>
       </c>
       <c r="R52" t="n">
-        <v>6277856</v>
+        <v>6277717</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6810,24 +6816,14 @@
           <t>Torslunda</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>36d18be7-cf1b-410b-94f1-5263d1175608</t>
-        </is>
-      </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Två hopväxta stammar</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6838,32 +6834,37 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118348</t>
+          <t>https://artportalen.se/Sighting/3440372</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>106118349</v>
+        <v>106118348</v>
       </c>
       <c r="B53" t="n">
         <v>106813</v>
@@ -6902,10 +6903,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>592537</v>
+        <v>592552</v>
       </c>
       <c r="R53" t="n">
-        <v>6277806</v>
+        <v>6277856</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6932,7 +6933,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>b0c88e0a-0ecb-47cf-81a5-9ec55e773bfe</t>
+          <t>36d18be7-cf1b-410b-94f1-5263d1175608</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -6943,6 +6944,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2022-03-21</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Två hopväxta stammar</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6972,13 +6978,13 @@
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118349</t>
+          <t>https://artportalen.se/Sighting/106118348</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>106118350</v>
+        <v>106118349</v>
       </c>
       <c r="B54" t="n">
         <v>106813</v>
@@ -7013,14 +7019,14 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>592476</v>
+        <v>592537</v>
       </c>
       <c r="R54" t="n">
-        <v>6277657</v>
+        <v>6277806</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -7047,7 +7053,7 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>195e5dc7-1b1a-42dc-b2d9-e91e699d5598</t>
+          <t>b0c88e0a-0ecb-47cf-81a5-9ec55e773bfe</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
@@ -7087,33 +7093,33 @@
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106118350</t>
+          <t>https://artportalen.se/Sighting/106118349</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>3367715</v>
+        <v>106118350</v>
       </c>
       <c r="B55" t="n">
-        <v>106155</v>
+        <v>106813</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -7121,10 +7127,9 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>blomning</t>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7133,13 +7138,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>592474</v>
+        <v>592476</v>
       </c>
       <c r="R55" t="n">
-        <v>6277717</v>
+        <v>6277657</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7161,14 +7166,19 @@
           <t>Torslunda</t>
         </is>
       </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>195e5dc7-1b1a-42dc-b2d9-e91e699d5598</t>
+        </is>
+      </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2006-04-16</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2006-04-16</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7179,40 +7189,35 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/3367715</t>
+          <t>https://artportalen.se/Sighting/106118350</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>5024204</v>
+        <v>3367715</v>
       </c>
       <c r="B56" t="n">
-        <v>101325</v>
+        <v>106155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7220,24 +7225,29 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Torslund, Öl</t>
@@ -7274,12 +7284,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2006-04-15</t>
+          <t>2006-04-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2006-04-15</t>
+          <t>2006-04-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7304,7 +7314,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
@@ -7314,16 +7324,16 @@
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5024204</t>
+          <t>https://artportalen.se/Sighting/3367715</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>92513455</v>
+        <v>5024204</v>
       </c>
       <c r="B57" t="n">
-        <v>101326</v>
+        <v>101325</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7349,23 +7359,19 @@
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>592433</v>
+        <v>592474</v>
       </c>
       <c r="R57" t="n">
-        <v>6277710</v>
+        <v>6277717</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7389,12 +7395,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2006-04-15</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2006-04-15</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7403,39 +7409,42 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>ädellövskog</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr"/>
+          <t>Karl-göran Bringer</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92513455</t>
+          <t>https://artportalen.se/Sighting/5024204</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131773215</v>
+        <v>92513455</v>
       </c>
       <c r="B58" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7462,11 +7471,7 @@
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
@@ -7475,10 +7480,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>592508</v>
+        <v>592433</v>
       </c>
       <c r="R58" t="n">
-        <v>6277573</v>
+        <v>6277710</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7505,12 +7510,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7525,7 +7530,7 @@
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>hassel och grova ekar, en del klibbal</t>
+          <t>ädellövskog</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr"/>
@@ -7536,22 +7541,22 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Tommy Carlström, Thomas Gunnarsson, Ingela Carlström, Ulla-Britt Andersson</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131773215</t>
+          <t>https://artportalen.se/Sighting/92513455</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131773205</v>
+        <v>131773215</v>
       </c>
       <c r="B59" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7559,21 +7564,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7587,14 +7592,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>592466</v>
+        <v>592508</v>
       </c>
       <c r="R59" t="n">
-        <v>6277602</v>
+        <v>6277573</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7652,22 +7657,22 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+          <t>Tommy Carlström, Thomas Gunnarsson, Ingela Carlström, Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131773205</t>
+          <t>https://artportalen.se/Sighting/131773215</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131773199</v>
+        <v>131773205</v>
       </c>
       <c r="B60" t="n">
-        <v>101325</v>
+        <v>101324</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7675,16 +7680,16 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222783</v>
+        <v>222782</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gulsippa</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Anemone ranunculoides</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -7696,21 +7701,21 @@
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>592567</v>
+        <v>592466</v>
       </c>
       <c r="R60" t="n">
-        <v>6277523</v>
+        <v>6277602</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7774,59 +7779,62 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131773199</t>
+          <t>https://artportalen.se/Sighting/131773205</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>5462704</v>
+        <v>131773199</v>
       </c>
       <c r="B61" t="n">
-        <v>101079</v>
+        <v>101325</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>222815</v>
+        <v>222783</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Hålnunneört</t>
+          <t>Gulsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Corydalis cava</t>
+          <t>Anemone ranunculoides</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Schweigg. &amp; Körte</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>592474</v>
+        <v>592567</v>
       </c>
       <c r="R61" t="n">
-        <v>6277717</v>
+        <v>6277523</v>
       </c>
       <c r="S61" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7850,12 +7858,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2006-04-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2006-04-16</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7864,39 +7872,36 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AI61" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
+          <t>hassel och grova ekar, en del klibbal</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr">
-        <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5462704</t>
+          <t>https://artportalen.se/Sighting/131773199</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>77033617</v>
+        <v>5462704</v>
       </c>
       <c r="B62" t="n">
         <v>101079</v>
@@ -7925,23 +7930,24 @@
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torslunda kyrka väst, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>592562</v>
+        <v>592474</v>
       </c>
       <c r="R62" t="n">
-        <v>6277501</v>
+        <v>6277717</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7965,17 +7971,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
+          <t>2006-04-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2019-04-14</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>endast rödblommiga</t>
+          <t>2006-04-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7984,24 +7985,23 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>skogsdunge med ek, hassel och ask</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">
@@ -8011,16 +8011,16 @@
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77033617</t>
+          <t>https://artportalen.se/Sighting/5462704</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>92513436</v>
+        <v>77033617</v>
       </c>
       <c r="B63" t="n">
-        <v>101080</v>
+        <v>101079</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8047,23 +8047,19 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslunda kyrka väst, Öl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>592567</v>
+        <v>592562</v>
       </c>
       <c r="R63" t="n">
-        <v>6277523</v>
+        <v>6277501</v>
       </c>
       <c r="S63" t="n">
         <v>25</v>
@@ -8090,12 +8086,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2019-04-14</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2021-04-17</t>
+          <t>2019-04-14</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>endast rödblommiga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8110,7 +8111,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>ädellövskog</t>
+          <t>skogsdunge med ek, hassel och ask</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -8124,16 +8125,20 @@
           <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
-      <c r="AY63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/92513436</t>
+          <t>https://artportalen.se/Sighting/77033617</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>100502889</v>
+        <v>92513436</v>
       </c>
       <c r="B64" t="n">
         <v>101080</v>
@@ -8165,21 +8170,21 @@
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>592552</v>
+        <v>592567</v>
       </c>
       <c r="R64" t="n">
-        <v>6277509</v>
+        <v>6277523</v>
       </c>
       <c r="S64" t="n">
         <v>25</v>
@@ -8206,12 +8211,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2021-04-17</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8224,6 +8229,11 @@
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>ädellövskog</t>
+        </is>
+      </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
@@ -8238,58 +8248,62 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100502889</t>
+          <t>https://artportalen.se/Sighting/92513436</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>106121031</v>
+        <v>100502889</v>
       </c>
       <c r="B65" t="n">
-        <v>103403</v>
+        <v>101080</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>223246</v>
+        <v>222815</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Skogsalm</t>
+          <t>Hålnunneört</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Ulmus glabra</t>
+          <t>Corydalis cava</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Huds.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Schweigg. &amp; Körte</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>592415</v>
+        <v>592552</v>
       </c>
       <c r="R65" t="n">
-        <v>6277921</v>
+        <v>6277509</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8311,19 +8325,14 @@
           <t>Torslunda</t>
         </is>
       </c>
-      <c r="X65" t="inlineStr">
-        <is>
-          <t>fda9f1e5-a86b-46c3-be1d-97fd28e40e8e</t>
-        </is>
-      </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8332,37 +8341,34 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Thomas Johansson</t>
-        </is>
-      </c>
-      <c r="AY65" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106121031</t>
+          <t>https://artportalen.se/Sighting/100502889</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>5779785</v>
+        <v>106121031</v>
       </c>
       <c r="B66" t="n">
-        <v>103407</v>
+        <v>103403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8370,37 +8376,41 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>223248</v>
+        <v>223246</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lundalm</t>
+          <t>Skogsalm</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ulmus minor</t>
+          <t>Ulmus glabra</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Mill.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>Huds.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>592474</v>
+        <v>592415</v>
       </c>
       <c r="R66" t="n">
-        <v>6277717</v>
+        <v>6277921</v>
       </c>
       <c r="S66" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8422,14 +8432,19 @@
           <t>Torslunda</t>
         </is>
       </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>fda9f1e5-a86b-46c3-be1d-97fd28e40e8e</t>
+        </is>
+      </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2022-03-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8440,37 +8455,32 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>Ädellövskog</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+          <t>Thomas Johansson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>Inventering av Ölands kärlväxtflora.</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5779785</t>
+          <t>https://artportalen.se/Sighting/106121031</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>5784861</v>
+        <v>5779785</v>
       </c>
       <c r="B67" t="n">
         <v>103407</v>
@@ -8499,24 +8509,19 @@
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>592605</v>
+        <v>592474</v>
       </c>
       <c r="R67" t="n">
-        <v>6277859</v>
+        <v>6277717</v>
       </c>
       <c r="S67" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8540,17 +8545,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2007-07-23</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2007-07-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>ca 10 träd</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8570,12 +8570,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lissbeth Bringer</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr">
@@ -8585,58 +8585,59 @@
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/5784861</t>
+          <t>https://artportalen.se/Sighting/5779785</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>78870855</v>
+        <v>5784861</v>
       </c>
       <c r="B68" t="n">
-        <v>103450</v>
+        <v>103407</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>223253</v>
+        <v>223248</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Etternässla</t>
+          <t>Lundalm</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Urtica urens</t>
+          <t>Ulmus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Mill.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torslunda försöksstationen, Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>592617</v>
+        <v>592605</v>
       </c>
       <c r="R68" t="n">
-        <v>6277632</v>
+        <v>6277859</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8660,12 +8661,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2007-07-23</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2019-07-11</t>
+          <t>2007-07-23</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>ca 10 träd</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8674,24 +8680,23 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
       <c r="AI68" t="inlineStr">
         <is>
-          <t>fodermajsåker</t>
+          <t>Ädellövskog</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Lissbeth Bringer</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
@@ -8701,16 +8706,16 @@
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78870855</t>
+          <t>https://artportalen.se/Sighting/5784861</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>78870864</v>
+        <v>78870855</v>
       </c>
       <c r="B69" t="n">
-        <v>105657</v>
+        <v>103450</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8718,19 +8723,23 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>224063</v>
+        <v>223253</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Sydspärgel</t>
+          <t>Etternässla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Spergula arvensis subsp. arvensis</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>Urtica urens</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
@@ -8780,11 +8789,6 @@
           <t>2019-07-11</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>frön med papiller</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8818,50 +8822,54 @@
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/78870864</t>
+          <t>https://artportalen.se/Sighting/78870855</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>6453177</v>
+        <v>78870864</v>
       </c>
       <c r="B70" t="n">
-        <v>103403</v>
+        <v>105657</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>225046</v>
+        <v>224063</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Sydspärgel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
+          <t>Spergula arvensis subsp. arvensis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Torslund, Öl</t>
+          <t>Torslunda försöksstationen, Öl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>592474</v>
+        <v>592617</v>
       </c>
       <c r="R70" t="n">
-        <v>6277717</v>
+        <v>6277632</v>
       </c>
       <c r="S70" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8885,12 +8893,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2019-07-11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2007-02-13</t>
+          <t>2019-07-11</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>frön med papiller</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8899,23 +8912,24 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Ädellövskog</t>
+          <t>fodermajsåker</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer</t>
+          <t>Ulla-Britt Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+          <t>Ulla-Britt Andersson, Thomas Gunnarsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr">
@@ -8925,66 +8939,50 @@
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6453177</t>
+          <t>https://artportalen.se/Sighting/78870864</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130575404</v>
+        <v>6453177</v>
       </c>
       <c r="B71" t="n">
-        <v>56965</v>
+        <v>103403</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>232125</v>
+        <v>225046</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsgås</t>
+          <t>Vanlig skogsalm</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Anser fabalis</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Latham, 1787)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Skogsby, Öl</t>
+          <t>Torslund, Öl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>592512</v>
+        <v>592474</v>
       </c>
       <c r="R71" t="n">
-        <v>6277542</v>
+        <v>6277717</v>
       </c>
       <c r="S71" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -9008,22 +9006,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2007-02-13</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9034,80 +9022,90 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Ädellövskog</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Bengt E Larsson</t>
+          <t>Karl-göran Bringer</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Bengt E Larsson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
+          <t>Karl-göran Bringer, Lissbeth Bringer</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130575404</t>
+          <t>https://artportalen.se/Sighting/6453177</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131773213</v>
+        <v>130575404</v>
       </c>
       <c r="B72" t="n">
-        <v>84199</v>
+        <v>56965</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>232272</v>
+        <v>232125</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Skogsgås</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Anser fabalis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Latham, 1787)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Tors lund, Öl</t>
+          <t>Skogsby, Öl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>592508</v>
+        <v>592512</v>
       </c>
       <c r="R72" t="n">
-        <v>6277573</v>
+        <v>6277542</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9131,17 +9129,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>funnen av Ingela</t>
+          <t>2026-01-08</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9150,39 +9153,33 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>hassel och grova ekar, en del klibbal</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson</t>
+          <t>Bengt E Larsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+          <t>Bengt E Larsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131773213</t>
+          <t>https://artportalen.se/Sighting/130575404</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>6558759</v>
+        <v>131773213</v>
       </c>
       <c r="B73" t="n">
-        <v>89871</v>
+        <v>84199</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9190,37 +9187,48 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>236435</v>
+        <v>232272</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Droppklibbskivling</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Limacella guttata</t>
+          <t>Sarcoscypha austriaca</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Beck) Boud.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Tors lund, 300m V om Torslunda kyrka., Öl</t>
+          <t>Tors lund, Öl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>592529</v>
+        <v>592508</v>
       </c>
       <c r="R73" t="n">
-        <v>6277673</v>
+        <v>6277573</v>
       </c>
       <c r="S73" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9244,17 +9252,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>1992-09-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>1992-09-10</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Leg. Karl-Göran Bringer</t>
+          <t>funnen av Ingela</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9263,31 +9271,144 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Ek-hasselskog.</t>
+          <t>hassel och grova ekar, en del klibbal</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
+          <t>Ulla-Britt Andersson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla-Britt Andersson, Ingela Carlström, Thomas Gunnarsson, Tommy Carlström</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131773213</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>6558759</v>
+      </c>
+      <c r="B74" t="n">
+        <v>89871</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>236435</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Droppklibbskivling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Limacella guttata</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Pers. : Fr.) Konrad &amp; Maubl.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Tors lund, 300m V om Torslunda kyrka., Öl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>592529</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6277673</v>
+      </c>
+      <c r="S74" t="n">
+        <v>100</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Torslunda</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>1992-09-10</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>1992-09-10</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Leg. Karl-Göran Bringer</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Ek-hasselskog.</t>
+        </is>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
           <t>Tommy Knutsson</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
+      <c r="AX74" t="inlineStr">
         <is>
           <t>Via Tommy Knutsson</t>
         </is>
       </c>
-      <c r="AY73" t="inlineStr">
+      <c r="AY74" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
+      <c r="AZ74" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6558759</t>
         </is>
@@ -9367,6 +9488,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
